--- a/20260804_従業員管理_00_定義表.xlsx
+++ b/20260804_従業員管理_00_定義表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="定義表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'定義表'!$A$3:$K$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'定義表'!$A$3:$L$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -501,11 +501,12 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -518,7 +519,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>読む表です（記入はしません）。①L0リリース不可4件が1件でも不合格ならリリースしません ②L1 MVP必須37件のうち「不合格のときリリースは＝不可」は落とせません（条件付きGo可は手作業で代替可） ③L2次段階6件は判断に使いません。判定の記入は「確認表」、操作手順は「検証プラン」。</t>
+          <t>読む表です（記入はしません）。①L0リリース不可4件が1件でも不合格ならリリースしません ②L1 MVP必須37件のうち「不合格のときリリースは＝不可」は落とせません（条件付きGo可は手作業で代替可） ③L2次段階6件は判断に使いません。判定の記入は「01_確認表」、操作手順は「02_検証プラン」。</t>
         </is>
       </c>
     </row>
@@ -555,25 +556,30 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>対象画面</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>満たすべき状態</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>合格基準（定量）</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>実装の目安（どこまでできていれば合格か）</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>不合格のときリリースは</t>
         </is>
@@ -612,25 +618,30 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>すべての従業員に適用日付が付いている</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>適用日付がNULLの行=0件</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>移行時に初回レコードを過去日で生成。以降の変更はこの上に積む</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>条件付きGo不可（AC-03が担保できない）</t>
         </is>
@@ -669,25 +680,30 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>従業員詳細 → 従業員一覧</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>保存しても当日までは反映されない</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>当日時点での反映=0件（一覧は旧値のまま）</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>設定を「適用日付つきの履歴レコード」として保存し、参照時は基準日で有効行を解決する。上書きしない</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>不可（本機能の中心価値）</t>
         </is>
@@ -726,25 +742,30 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
+          <t>従業員詳細 → 従業員一覧</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>保存直後に反映される</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>反映の遅延=0（再読込で新値）</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>基準日&lt;=当日の行を有効として即時解決する</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>不可（通常の変更ができない）</t>
         </is>
@@ -783,25 +804,30 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
+          <t>従業員詳細／設定履歴</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>過去の履歴が書き換わらない</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>履歴が1行増え、既存行の差分=0</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>履歴テーブルはINSERTのみ。UPDATE/DELETEを行わない</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>不可（AC-03が連鎖して壊れる）</t>
         </is>
@@ -840,25 +866,30 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>変更の経路が記録される</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>4種すべてが記録・絞り込み可能</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>履歴に変更ソース列を持ち、更新経路ごとに値を入れる</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>不可（数字の異常時に切り分けられない）</t>
         </is>
@@ -897,25 +928,30 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
+          <t>従業員設定履歴</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>「いつから効くか」と「いつ操作したか」が別々に残る</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>予約行で 変更反映日時 ≠ 編集日時</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>履歴に適用日付と作成日時の2カラムを持つ</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>不可（監査・顧客説明に答えられない）</t>
         </is>
@@ -954,25 +990,30 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
+          <t>設定インポート／従業員一覧</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>同じ従業員コードが二重に登録されない</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>二重登録=0件（2回目は更新・件数増加なし）</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>従業員コードに一意制約。取込はコードをキーにupsert。CSV内の重複行は事前に検出</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>不可（人件費が二重計上されAC-11が壊れる）</t>
         </is>
@@ -1011,25 +1052,30 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
+          <t>従業員登録／従業員詳細</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>ヘルプ先ごとに別々の交通費を設定できる</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>選んだ店舗数ぶんの入力欄が出る（EMP-001＝2件：S02=700・S03=900）。1つにまとめられない</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>従業員×ヘルプ先店舗×交通費 を多対多で保持する。従業員に1つの値だけを持たせる実装は不可</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>不可（AC-15の店舗別計上が成立せず、遠い店ほど持ち出しになる）</t>
         </is>
@@ -1068,25 +1114,30 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
+          <t>人件費実績（月別・実績）</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>店舗別の合計が全社の実績給与と一致する</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>店舗5店の合計 − 全社 = 0円（1,461,312円）</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>ヘルプ人件費を「実績給与×ヘルプ時間÷総労働時間」で按分し、端数を所属店舗に寄せる（判断9）。加算のみの実装は不可</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="L12" s="8" t="inlineStr">
         <is>
           <t>★中止（店舗別PLが使えない）</t>
         </is>
@@ -1125,25 +1176,30 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
+          <t>従業員一覧／設定履歴</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>適用日を迎えたら自動で切り替わる</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>適用日00:00以降に新値・ステータスが「適用中」</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>日次バッチまたは参照時解決のいずれかで、適用日到来を人手なしに反映する</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>不可（毎日手作業になる）</t>
         </is>
@@ -1182,25 +1238,30 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別・実績）</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>実績給与が算式の計算値と一致する</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>全行で差分=0円（EMP-001=338,000／EMP-002=285,250／EMP-003=144,000／EMP-005=382,812／EMP-007=311,250）</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>実績給与＝概算給与＋深夜残業代＋みなし超過残業代。交通費は含めない</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>不可（数字の根拠が説明できない）</t>
         </is>
@@ -1239,25 +1300,30 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別・概算）</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>所定労働日割で按分される</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>332,727円（320,000×8/22＋340,000×14/22）</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>判断1＝所定労働日割。分母は当月の所定労働日数。暦日割の実装は不可</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>不可（予約機能が実用にならない）</t>
         </is>
@@ -1296,25 +1362,30 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別・概算）</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>単価×所定労働時間になる</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>144,000円（差分0）</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>時給者は日割り按分ではなく、各勤務日の有効単価で積む</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>不可（概算が使えない）</t>
         </is>
@@ -1353,25 +1424,30 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（日別）／月別</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>働いた店舗・その日の有効単価で計算される</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>按分額が実績給与×ヘルプ時間÷総労働時間と一致</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>日別の勤務店舗を保持し、店舗別集計時に振り替える</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>不可（店舗別PLが実態とずれる）</t>
         </is>
@@ -1410,25 +1486,30 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別・日別）</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>交通費が独立費目として一意に計上される</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>実績給与に交通費を含まない／通勤は所属店舗・ヘルプ先は応援先に計上（店舗別合計100,000円）</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>判断6＝独立列。給与とは別カラムで持ち、総支給額＝給与＋交通費で表示</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>不可（人件費の総額がずれる）</t>
         </is>
@@ -1467,25 +1548,30 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>締め済みの月の数字が動かない</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>当月の実績給与・総労働時間の差分=0円</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="K19" s="8" t="inlineStr">
         <is>
           <t>締めフラグを持ち、締め済み期間は再計算をスキップする（設定変更・勤怠取込の両方）。スナップショットで固定</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="L19" s="8" t="inlineStr">
         <is>
           <t>★中止（締めの意味が消える）</t>
         </is>
@@ -1524,25 +1610,30 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>保留されていた変更が反映されて再計算される</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>解除後の実績給与＝改定を反映した計算値（差分0円）</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>解除で締めフラグを落とし、再計算をキューに入れる</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>不可（誤りを修正できない）</t>
         </is>
@@ -1581,25 +1672,30 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>締めは月別タブにのみ表示される</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>日別タブでの表示=0</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>日別タブに締めUIを置かない</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（誤解を招くが実害は小さい）</t>
         </is>
@@ -1638,25 +1734,30 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>実行前に確認が入る</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>確認モーダル=各1回</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>締め・解除ともに確認を挟む</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（誤操作リスクは残る）</t>
         </is>
@@ -1695,25 +1796,30 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>従業員詳細</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>警告が出て、黙って無視されない</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>警告なしの保存=0件</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>締め済み期間への適用を検出して警告。既定は将来適用へ寄せる</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>不可（支払額と乖離する）</t>
         </is>
@@ -1752,25 +1858,30 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>店長は締めを実行できない</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>店長での締め実行=0件（ボタン非表示または拒否）</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>締めAPIを会社スコープ権限で制限。画面側だけで隠さない</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>不可（月次が店舗ごとに分断される）</t>
         </is>
@@ -1809,25 +1920,30 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>KOT形式のCSVが全行取り込める</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>取込成功=3行</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>ヘッダー名で列を解決。テンプレートDLの列と一致させる</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>不可（導入時に手入力になる）</t>
         </is>
@@ -1866,25 +1982,30 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>表記ゆれのヘッダーでも取り込める</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>取込成功=3行</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>列マッピングで吸収する（コードに列名を埋め込まない）</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>不可（ジョブカン顧客の導入が止まる）</t>
         </is>
@@ -1923,25 +2044,30 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>異常が検出され、不正な値が登録されない</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>4行すべて検出（見逃し=0）</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>コード欠落／負値／未登録店舗／型不正／未定義の雇用区分をサーバ側で検証</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>不可（マスタが壊れ人件費が狂う）</t>
         </is>
@@ -1980,25 +2106,30 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>保存して再利用できる</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>選択時の手入力=0項目</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>マッピングを保存・適用できる。開発なしで新形式に対応できる</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（都度マッピングで代替）</t>
         </is>
@@ -2037,25 +2168,30 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>選んだ項目だけが出力される</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>出力の列＝チェックした項目（過不足=0列）</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>選択した列のみを生成する（固定フォーマットにしない）</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>不可（不要な給与情報が渡し先に漏れる）</t>
         </is>
@@ -2094,25 +2230,30 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>対象ごとにファイルが分かれる</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>ファイル数=2</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>対象ごとにファイルを生成する</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（手作業で分割）</t>
         </is>
@@ -2151,25 +2292,30 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>出力されず警告が出る</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>未選択での出力=0件</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>出力前に選択状態を検証する</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可</t>
         </is>
@@ -2208,25 +2354,30 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
+          <t>設定・実績エクスポート</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>文字化けしない</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>文字化け=0箇所</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>BOM付きUTF-8で出力する</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>不可（外部提出に使えない）</t>
         </is>
@@ -2265,25 +2416,30 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>サイドバー</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>2グループ7項目が表示される</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>欠落=0</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>閲覧・管理3／データ連携4でグループ化</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>不可（画面に到達できない）</t>
         </is>
@@ -2322,25 +2478,30 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
+          <t>全画面</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>仕様どおりに画面が繋がる</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>不通=0</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>キャンセル・戻る・エラー時の遷移を含めて実装する</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>不可（フローが途中で切れる）</t>
         </is>
@@ -2379,25 +2540,30 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>従業員一覧／設定履歴</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>フィルタで対象を絞り込める</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>各条件で絞り込みが効く（無反応=0）</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>1段目=絞り込み、2段目=対象データとして独立に効かせる</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（件数が少ないうちは実害小）</t>
         </is>
@@ -2436,25 +2602,30 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
+          <t>従業員一覧／従業員詳細</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>確認を経てのみ削除される</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>確認なしの削除=0件、キャンセル時の削除=0件</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>削除前に確認ダイアログ。キャンセルでリクエストを送らない</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>不可（誤操作で過去の紐付けが失われる）</t>
         </is>
@@ -2493,25 +2664,30 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
+          <t>従業員詳細（給与実績）</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>画面が変わっても同じ数字が出る</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>同一従業員・同一月で差分=0円</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>同じ集計ロジックを共有する（画面ごとに別計算をしない）</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（説明コストが増える）</t>
         </is>
@@ -2550,25 +2726,30 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
+          <t>人件費実績／設定履歴／従業員詳細</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>表示中の内容どおりに出力される</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>出力の行・列＝画面の表示（差分0）</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>出力は画面の絞り込み条件を引き継ぐ（全件出力にしない）</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可</t>
         </is>
@@ -2607,25 +2788,30 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>開始行を指定すれば取り込める</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>取込成功=全行</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>ヘッダー行・データ開始行・開始列を指定できる</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（顧客にCSV加工を依頼する運用で代替）</t>
         </is>
@@ -2664,25 +2850,30 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>取り込んだ元データを確認できる</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>設定・実績とも参照可能</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>取込ファイルと取込結果を保存し、画面から参照できる</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>条件付きGo可（DBを直接見る運用で代替）</t>
         </is>
@@ -2721,25 +2912,30 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>設定インポート</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>途中で失敗しても中途半端な状態が残らない</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>部分登録の残存=0件</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>全体をトランザクションで囲む（全体拒否）か、行単位で結果を明示する。どちらでも可だが挙動を固定する</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>不可（どこまで入ったか分からず復旧できない）</t>
         </is>
@@ -2778,25 +2974,30 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>従業員登録</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
           <t>操作＋実装レビュー</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>必須が欠けたまま保存も遷移もしない</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>未入力での登録成功=0件、遷移=0件</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>サーバ側でも必須チェック（画面側だけにしない）。エラー時は同一画面に留まる</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>不可（締め時に止まる従業員が生まれる）</t>
         </is>
@@ -2835,25 +3036,30 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
+          <t>従業員一覧</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>移行後も既存の従業員が同じ内容で見える</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>件数の増減=0／12項目の差分=0</t>
         </is>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="K43" s="8" t="inlineStr">
         <is>
           <t>移行スクリプトが既存レコードを1対1で新モデルへ写像する。項目の欠落・型変換の失敗が0件</t>
         </is>
       </c>
-      <c r="K43" s="8" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr">
         <is>
           <t>★中止（既存顧客のマスタが壊れる）</t>
         </is>
@@ -2892,25 +3098,30 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>移行しても過去月の人件費が1円も変わらない</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>3か月とも差分=0円</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr">
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>移行時に各従業員へ「過去日の初回適用レコード」を必ず付与し、過去月の再計算を走らせない</t>
         </is>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="L44" s="8" t="inlineStr">
         <is>
           <t>★中止（この機能の存在意義が消える）</t>
         </is>
@@ -2949,25 +3160,30 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
+          <t>人件費実績／従業員詳細</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>切替が他画面に影響しない</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="J45" s="10" t="inlineStr">
         <is>
           <t>他画面の表示モードが変わらない</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>表示モードを画面ローカルに持つ</t>
         </is>
       </c>
-      <c r="K45" s="10" t="inlineStr">
+      <c r="L45" s="10" t="inlineStr">
         <is>
           <t>影響なし</t>
         </is>
@@ -3006,25 +3222,30 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>事前に警告が出る</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>警告表示=1回</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>締め実行時に設定の欠落を検出して警告（「従業員設定確定」廃止の代替）</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr">
+      <c r="L46" s="10" t="inlineStr">
         <is>
           <t>影響なし（次リリースで対応）</t>
         </is>
@@ -3063,25 +3284,30 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>編集・削除・一括登録ができる</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>いずれも成功（失敗=0）</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>テンプレートのCRUDとCSVでの一括登録</t>
         </is>
       </c>
-      <c r="K47" s="10" t="inlineStr">
+      <c r="L47" s="10" t="inlineStr">
         <is>
           <t>影響なし</t>
         </is>
@@ -3120,25 +3346,30 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>競合が制御される</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="J48" s="10" t="inlineStr">
         <is>
           <t>不整合=0件</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>締めに排他制御を入れる</t>
         </is>
       </c>
-      <c r="K48" s="10" t="inlineStr">
+      <c r="L48" s="10" t="inlineStr">
         <is>
           <t>影響なし（担当は通常1〜2名）</t>
         </is>
@@ -3177,25 +3408,30 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
+          <t>人件費実績（月別）</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>実行者と日時が記録される</t>
         </is>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="J49" s="10" t="inlineStr">
         <is>
           <t>解除の記録=1件/回</t>
         </is>
       </c>
-      <c r="J49" s="10" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>解除ログを保存する</t>
         </is>
       </c>
-      <c r="K49" s="10" t="inlineStr">
+      <c r="L49" s="10" t="inlineStr">
         <is>
           <t>影響なし（現状はT-S05の所見で代替）</t>
         </is>
@@ -3234,35 +3470,40 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
+          <t>従業員一覧／設定インポート</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
           <t>操作で確認</t>
         </is>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>実用的な速度で動く</t>
         </is>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>実務上支障のない時間</t>
         </is>
       </c>
-      <c r="J50" s="10" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>ページング・一括取込の最適化</t>
         </is>
       </c>
-      <c r="K50" s="10" t="inlineStr">
+      <c r="L50" s="10" t="inlineStr">
         <is>
           <t>影響なし（リリース後に計測）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:K50"/>
+  <autoFilter ref="A3:L50"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/20260804_従業員管理_00_定義表.xlsx
+++ b/20260804_従業員管理_00_定義表.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="定義表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'定義表'!$A$3:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'定義表'!$A$3:$L$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -512,14 +512,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>従業員管理 受入条件 定義表 ─ 何を満たせば合格か（47条件）</t>
+          <t>従業員管理 受入条件 定義表 ─ 何を満たせば合格か（51条件）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>読む表です（記入はしません）。①L0リリース不可4件が1件でも不合格ならリリースしません ②L1 MVP必須37件のうち「不合格のときリリースは＝不可」は落とせません（条件付きGo可は手作業で代替可） ③L2次段階6件は判断に使いません。判定の記入は「01_確認表」、操作手順は「02_検証プラン」。</t>
+          <t>読む表です（記入はしません）。①L0リリース不可が1件でも不合格ならリリースしません ②L1 MVP必須のうち「不合格のときリリースは＝不可」は落とせません（条件付きGo可は手作業で代替可） ③L2次段階は判断に使いません。判定の記入は「01_確認表」、操作手順は「02_検証プラン」。</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>仕様どおりに画面が繋がる</t>
+          <t>仕様書 第2部の遷移どおりに画面が繋がる（取込データ⇄人件費実績の相互導線を含む）</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -3499,8 +3499,256 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>実装M2 計算エンジン</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>V2 数字が実態を表す</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>実績値の源泉</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>AC-48</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>入出力：勤怠実績を取り込める</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>人件費実績</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>操作で確認</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>「実績データ取込」で勤怠実績が取り込まれ、人件費実績に反映されること</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>取込後に実績モードの金額が表示される（未反映=0件）。取込中は画面を操作できない</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>取込処理を非同期で実行し、進捗を返す。処理中は締めなど後続の操作を受け付けない</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>不可（実績の数字が出ず、締めも意味を持たない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>実装M1 データ基盤</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>V1 数字が動かない</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>P1 過去が動く</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>原則①：どの入口でも履歴が残る</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>人件費実績（設定編集モーダル）／従業員詳細</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>操作＋実装レビュー</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>どの入口から設定を編集しても、適用日付と設定変更履歴が同じように記録されること</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>モーダル経由・詳細経由のどちらでも履歴が1行増える（記録されない編集=0件）。変更ソースも記録される</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>設定更新の処理を1箇所に集約し、両方の画面から同じ処理を呼ぶ。画面ごとに別の更新処理を持たない</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>不可（片方だけ履歴が残らないと変更を追えない期間ができ、AC-07・AC-03に連鎖）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>L1 MVP必須</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>実装M4 画面・入出力</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>V3 自分で運用できる</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>取込事故を防ぐ</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>AC-50</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>データ保全：取り込む前に気づける</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>設定取込データ／実績取込データ</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>操作で確認</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>取り込む前に、内容のプレビューと前回との差分を確認できること</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>プレビューで取込内容が表示される。前回差分で「前回◯◯→新規◯◯」の形式で差が表示される（差分が出ない=0件）</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>前回の取込内容を保持し、項目単位で新旧を比較して差だけを提示する</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>条件付きGo可（取込後に人件費実績で確認する運用で代替。ただし気づくのが遅れる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>L2 次段階</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>（次リリース）</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>V3 自分で運用できる</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>K4 開発待ちになる</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>AC-51</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>入出力：マッピングの一括運用</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>列マッピングテンプレート</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>操作で確認</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>マッピング表をテンプレートでダウンロードし、行を追加・更新できること</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>テンプレートDL・行追加・更新がいずれも動作（失敗=0）</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>マッピング行のCRUDとテンプレートの入出力</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>影響なし（1件ずつ設定する運用で代替）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:L50"/>
+  <autoFilter ref="A3:L54"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>

--- a/20260804_従業員管理_00_定義表.xlsx
+++ b/20260804_従業員管理_00_定義表.xlsx
@@ -2121,7 +2121,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>選択時の手入力=0項目</t>
+          <t>保存済みテンプレート選択時の手入力=0項目。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -3728,17 +3728,17 @@
       </c>
       <c r="I54" s="10" t="inlineStr">
         <is>
-          <t>マッピング表をテンプレートでダウンロードし、行を追加・更新できること</t>
+          <t>マッピング表をテンプレートでダウンロードし、記入したファイルをアップロードして一括登録できること。行の追加と更新もできること</t>
         </is>
       </c>
       <c r="J54" s="10" t="inlineStr">
         <is>
-          <t>テンプレートDL・行追加・更新がいずれも動作（失敗=0）</t>
+          <t>テンプレートDL・アップロード（CSV最大10MB）・行を追加・更新する がいずれも動作（失敗=0）。10MB超は拒否</t>
         </is>
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>マッピング行のCRUDとテンプレートの入出力</t>
+          <t>マッピング行のCRUDと、テンプレートCSVの入出力（アップロードは上限を設ける）</t>
         </is>
       </c>
       <c r="L54" s="10" t="inlineStr">
